--- a/core/modules/poi/src/test/resources/org/onetwo/common/excel/excel-template.xlsx
+++ b/core/modules/poi/src/test/resources/org/onetwo/common/excel/excel-template.xlsx
@@ -1,85 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mydev\workspace\onetwo\labs\test-onetwo\src\test\resources\org\onetwo\common\excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="555" windowWidth="21255" windowHeight="9225"/>
+    <workbookView windowWidth="24460" windowHeight="9920"/>
   </bookViews>
   <sheets>
     <sheet name="按线路统计，2014-10-20 至 2014-11-25" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'按线路统计，2014-10-20 至 2014-11-25'!$A$5:$J$12</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
-  <si>
-    <t>票价形式</t>
-  </si>
-  <si>
-    <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>线路名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刷卡宗数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>优惠金额(元)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>线路</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>市民卡（普通实名卡和不记名卡）刷卡数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>核对意见</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>清远市民卡公司（签章）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公交公司（签章）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">           年  月  日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>附近二</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刷卡金额(元)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 第 1  页 共 2 页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
@@ -87,9 +52,8 @@
         <b/>
         <u/>
         <sz val="16"/>
-        <color indexed="8"/>
+        <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -99,9 +63,8 @@
       <rPr>
         <b/>
         <sz val="16"/>
-        <color indexed="8"/>
+        <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -112,76 +75,139 @@
         <b/>
         <u/>
         <sz val="16"/>
-        <color indexed="8"/>
+        <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> ${month} </t>
+      <t xml:space="preserve"> ${now.month} </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="16"/>
-        <color indexed="8"/>
+        <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>月清远市市民卡公交刷卡数据核对表</t>
+      <t>月公交刷卡数据核对表</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">共 ${lineCount} 条线路 ${busCount}  辆车    </t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 第 1  页 共 2 页</t>
+  </si>
+  <si>
+    <t>线路</t>
+  </si>
+  <si>
+    <t>市民卡（普通实名卡和不记名卡）刷卡数据</t>
+  </si>
+  <si>
+    <t>${lineCount}</t>
+  </si>
+  <si>
+    <t>${busCount}</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>线路名称</t>
+  </si>
+  <si>
+    <t>票价形式</t>
+  </si>
+  <si>
+    <t>刷卡宗数</t>
+  </si>
+  <si>
+    <t>刷卡金额(元)</t>
+  </si>
+  <si>
+    <t>优惠金额(元)</t>
+  </si>
+  <si>
+    <t>[row:list datalist as data, index]</t>
+  </si>
+  <si>
+    <t>${index}</t>
   </si>
   <si>
     <t>${data.linename}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>${#f.format(data.money)}</t>
   </si>
   <si>
     <t>[/row:list]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>${totalLabel}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[row:list datalist as data, index]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>${index}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>${#f.format(data.money)}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>核对意见</t>
+  </si>
+  <si>
+    <t>公司（签章）</t>
+  </si>
+  <si>
+    <t>公交公司（签章）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           年  月  日</t>
+  </si>
+  <si>
+    <t>测试</t>
+  </si>
+  <si>
+    <t>${身份证}</t>
+  </si>
+  <si>
+    <t>${姓名}</t>
+  </si>
+  <si>
+    <t>${地址}</t>
+  </si>
+  <si>
+    <t>${电话}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -190,51 +216,378 @@
       <sz val="16"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <u/>
       <sz val="16"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -243,6 +596,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -284,6 +646,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -293,37 +679,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -349,6 +722,19 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom style="thin">
@@ -358,15 +744,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -378,132 +755,397 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -552,7 +1194,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -587,7 +1229,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -790,14 +1432,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
     <col min="2" max="2" width="12.875" customWidth="1"/>
@@ -805,195 +1447,259 @@
     <col min="5" max="5" width="12.75" customWidth="1"/>
     <col min="6" max="6" width="14.625" customWidth="1"/>
     <col min="7" max="7" width="15.75" customWidth="1"/>
+    <col min="8" max="8" width="18.9038461538462" customWidth="1"/>
     <col min="9" max="9" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="24"/>
+    <row r="1" ht="26.25" customHeight="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
+    <row r="2" ht="36" customHeight="1" spans="1:7">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
     </row>
-    <row r="3" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
+    <row r="3" ht="39.75" customHeight="1" spans="1:7">
+      <c r="A3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
       <c r="E3" s="22" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
     </row>
-    <row r="4" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="25" t="s">
+    <row r="4" ht="41.25" customHeight="1" spans="1:10">
+      <c r="A4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
+      <c r="I4" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <f>SUM(H4:I4)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="4" t="s">
+    <row r="5" ht="37.5" customHeight="1" spans="1:7">
+      <c r="A5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>4</v>
+      <c r="G5" s="26" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="9" t="s">
+    <row r="6" ht="18" customHeight="1" spans="1:10">
+      <c r="A6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:10">
+      <c r="A7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:10">
+      <c r="A8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:10">
+      <c r="A9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11">
+        <v>320970</v>
+      </c>
+      <c r="F9" s="28">
+        <v>627764.75</v>
+      </c>
+      <c r="G9" s="28">
+        <v>85604.28</v>
+      </c>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
     </row>
-    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="9" t="s">
+    <row r="10" ht="116.25" customHeight="1" spans="1:7">
+      <c r="A10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:7">
+      <c r="A11" s="16"/>
+      <c r="B11" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="18"/>
+      <c r="G11" s="19"/>
     </row>
-    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-    </row>
-    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1">
-        <v>320970</v>
-      </c>
-      <c r="F9" s="6">
-        <v>627764.75</v>
-      </c>
-      <c r="G9" s="6">
-        <v>85604.28</v>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-    </row>
-    <row r="10" spans="1:10" ht="116.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="16"/>
-      <c r="B11" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20"/>
-    </row>
-    <row r="12" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="17"/>
+    <row r="12" ht="30.75" customHeight="1" spans="1:7">
+      <c r="A12" s="20"/>
       <c r="B12" s="21" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C12" s="22"/>
       <c r="D12" s="23"/>
       <c r="E12" s="21" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:G3"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="E4:G4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="E10:G10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:G12"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="E12:G12"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>